--- a/Base/Metas/Metas-2023.xlsx
+++ b/Base/Metas/Metas-2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\!Preparacao_curso\Base\Metas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zero\Desktop\Curso-PowerBI\Base\Metas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D65D393-D48D-45D8-B9F9-99B4083A81A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F220FAD-A08E-4C12-B5AE-8A08237753D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E2E1667E-2445-4855-8284-3293EB263DCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E2E1667E-2445-4855-8284-3293EB263DCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Metas" sheetId="5" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -342,7 +340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -745,17 +743,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5705D43-09F0-4AE8-B853-E52B7D4FAE3E}">
   <dimension ref="A1:AB74"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="44.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -841,7 +839,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -900,7 +898,7 @@
         <v>10100</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U4">
         <v>505000</v>
@@ -927,7 +925,7 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -1013,7 +1011,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -1099,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1185,7 +1183,7 @@
         <v>707000</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1271,7 +1269,7 @@
         <v>1010000</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -1357,7 +1355,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:28">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1443,7 +1441,7 @@
         <v>404000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:28">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1529,7 +1527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:28">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1613,7 @@
         <v>1010000</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:28">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1701,7 +1699,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:28">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1787,7 +1785,7 @@
         <v>40400</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:28">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -1873,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:28">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1959,7 +1957,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:28">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -2045,7 +2043,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:28">
       <c r="A18" t="s">
         <v>14</v>
       </c>
@@ -2131,7 +2129,7 @@
         <v>303000</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -2217,7 +2215,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:28">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -2303,7 +2301,7 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:28">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -2389,7 +2387,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:28">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -2475,7 +2473,7 @@
         <v>505000</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:28">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2561,7 +2559,7 @@
         <v>70700</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:28">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -2647,7 +2645,7 @@
         <v>40400</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:28">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2733,7 +2731,7 @@
         <v>50500</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:28">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -2819,7 +2817,7 @@
         <v>15150</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:28">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -2905,7 +2903,7 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:28">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2991,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:28">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -3077,7 +3075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:28">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -3163,7 +3161,7 @@
         <v>50500</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:28">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -3249,7 +3247,7 @@
         <v>101000</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:28">
       <c r="A32" t="s">
         <v>28</v>
       </c>
@@ -3335,7 +3333,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:28">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -3421,7 +3419,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:28">
       <c r="A34" t="s">
         <v>30</v>
       </c>
@@ -3507,7 +3505,7 @@
         <v>40400</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:28">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -3593,7 +3591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:28">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -3679,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:28">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -3765,7 +3763,7 @@
         <v>50500</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:28">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -3851,7 +3849,7 @@
         <v>30300</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:28">
       <c r="A39" t="s">
         <v>35</v>
       </c>
@@ -3937,7 +3935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:28">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -4023,7 +4021,7 @@
         <v>40400</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:28">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -4109,7 +4107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:28">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -4195,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:28">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -4281,7 +4279,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:28">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -4367,7 +4365,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:28">
       <c r="A45" t="s">
         <v>41</v>
       </c>
@@ -4453,7 +4451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:28">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -4539,7 +4537,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:28">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -4625,7 +4623,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:28">
       <c r="A48" t="s">
         <v>44</v>
       </c>
@@ -4711,7 +4709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:28">
       <c r="A49" t="s">
         <v>45</v>
       </c>
@@ -4797,7 +4795,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:28">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -4883,7 +4881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:28">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -4969,7 +4967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:28">
       <c r="A52" t="s">
         <v>48</v>
       </c>
@@ -5055,7 +5053,7 @@
         <v>20200</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:28">
       <c r="A53" t="s">
         <v>49</v>
       </c>
@@ -5141,7 +5139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:28">
       <c r="A54" t="s">
         <v>50</v>
       </c>
@@ -5227,7 +5225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:28">
       <c r="A55" t="s">
         <v>51</v>
       </c>
@@ -5313,7 +5311,7 @@
         <v>30300</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:28">
       <c r="A56" t="s">
         <v>52</v>
       </c>
@@ -5399,7 +5397,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:28">
       <c r="A57" t="s">
         <v>53</v>
       </c>
@@ -5485,7 +5483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:28">
       <c r="A58" t="s">
         <v>54</v>
       </c>
@@ -5571,7 +5569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:28">
       <c r="A59" t="s">
         <v>55</v>
       </c>
@@ -5657,7 +5655,7 @@
         <v>50500</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:28">
       <c r="A60" t="s">
         <v>56</v>
       </c>
@@ -5743,7 +5741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:28">
       <c r="A61" t="s">
         <v>57</v>
       </c>
@@ -5829,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:28">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -5915,7 +5913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:28">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -6001,7 +5999,7 @@
         <v>10100</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:28">
       <c r="A64" t="s">
         <v>60</v>
       </c>
@@ -6087,7 +6085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:28">
       <c r="A65" t="s">
         <v>61</v>
       </c>
@@ -6173,7 +6171,7 @@
         <v>50500</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:28">
       <c r="A66" t="s">
         <v>62</v>
       </c>
@@ -6259,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:28">
       <c r="A67" t="s">
         <v>63</v>
       </c>
@@ -6345,7 +6343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:28">
       <c r="A68" t="s">
         <v>64</v>
       </c>
@@ -6431,7 +6429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:28">
       <c r="A69" t="s">
         <v>65</v>
       </c>
@@ -6517,7 +6515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:28">
       <c r="A70" t="s">
         <v>66</v>
       </c>
@@ -6603,7 +6601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:28">
       <c r="A71" t="s">
         <v>67</v>
       </c>
@@ -6689,7 +6687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:28">
       <c r="A72" t="s">
         <v>68</v>
       </c>
@@ -6775,7 +6773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:28">
       <c r="A73" t="s">
         <v>69</v>
       </c>
@@ -6861,7 +6859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:28">
       <c r="A74" t="s">
         <v>70</v>
       </c>
